--- a/IFS Functions.xlsx
+++ b/IFS Functions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E8DA0E-65C7-4BDE-8ABD-CE971EF927C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFC831E-76E7-4FB1-8543-5EEDD10E339F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{7F0EFD1D-25ED-4FB0-BBDC-4DF1F93FAE83}"/>
   </bookViews>
@@ -1099,6 +1099,10 @@
       <c r="N10" t="s">
         <v>48</v>
       </c>
+      <c r="O10">
+        <f>COUNTIFS(F2:F21,F21,E2:E21,E2)</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11">
